--- a/artfynd/A 60406-2025 artfynd.xlsx
+++ b/artfynd/A 60406-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130325720</v>
+        <v>130325716</v>
       </c>
       <c r="B2" t="n">
-        <v>8440</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,7 +709,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662322</v>
+        <v>662361</v>
       </c>
       <c r="R2" t="n">
-        <v>6557792</v>
+        <v>6557758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130325716</v>
+        <v>130325720</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,7 +826,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662361</v>
+        <v>662322</v>
       </c>
       <c r="R3" t="n">
-        <v>6557758</v>
+        <v>6557792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 60406-2025 artfynd.xlsx
+++ b/artfynd/A 60406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325716</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130325720</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>